--- a/Team_Tasks.xlsx
+++ b/Team_Tasks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ELE_4\Prototype\Robotic_Car_TeamC1-HSHL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277E8E29-28C2-4A2F-8E6A-E10AB1EF3162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B389B3-6C67-415A-9544-1F2B382A33B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>Milestone</t>
   </si>
@@ -91,17 +91,41 @@
     <t>Servo-Motor&amp; Holder</t>
   </si>
   <si>
-    <t>Calculation printing time</t>
-  </si>
-  <si>
     <t>Creality print</t>
+  </si>
+  <si>
+    <t>Edit Diagrams related</t>
+  </si>
+  <si>
+    <t>Fast Voltage handling</t>
+  </si>
+  <si>
+    <t>Button design</t>
+  </si>
+  <si>
+    <t>UPPAAL</t>
+  </si>
+  <si>
+    <t>Soldering</t>
+  </si>
+  <si>
+    <t>Coding (Lane-Follow)</t>
+  </si>
+  <si>
+    <t>latex Doc_Writing</t>
+  </si>
+  <si>
+    <t>Coding (Colors)</t>
+  </si>
+  <si>
+    <t>ColorSensor holder</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,21 +150,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,8 +213,13 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -311,13 +347,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -352,49 +402,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="3" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="7" borderId="9" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="8" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -677,12 +740,12 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.36328125" style="2" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.36328125" style="2" bestFit="1" customWidth="1"/>
@@ -696,34 +759,34 @@
     <col min="18" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="21" t="s">
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="23"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27"/>
     </row>
     <row r="2" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -791,7 +854,7 @@
       <c r="D3" s="9">
         <v>45763</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="12">
         <v>45761</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -803,7 +866,7 @@
       <c r="H3" s="9">
         <v>45763</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="12">
         <v>45761</v>
       </c>
       <c r="J3" s="8" t="s">
@@ -815,7 +878,7 @@
       <c r="L3" s="9">
         <v>45763</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="14">
         <v>45761</v>
       </c>
       <c r="N3" s="8" t="s">
@@ -827,7 +890,9 @@
       <c r="P3" s="9">
         <v>45771</v>
       </c>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="12">
+        <v>45771</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
@@ -842,7 +907,7 @@
       <c r="D4" s="9">
         <v>45763</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="12">
         <v>45761</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -854,7 +919,7 @@
       <c r="H4" s="9">
         <v>45763</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="12">
         <v>45761</v>
       </c>
       <c r="J4" s="8" t="s">
@@ -864,7 +929,9 @@
       <c r="L4" s="9">
         <v>45771</v>
       </c>
-      <c r="M4" s="8"/>
+      <c r="M4" s="14">
+        <v>45771</v>
+      </c>
       <c r="N4" s="8" t="s">
         <v>9</v>
       </c>
@@ -872,7 +939,9 @@
       <c r="P4" s="9">
         <v>45771</v>
       </c>
-      <c r="Q4" s="8"/>
+      <c r="Q4" s="12">
+        <v>45771</v>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
@@ -887,41 +956,107 @@
       <c r="D5" s="9">
         <v>45763</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="12">
         <v>45761</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="H5" s="9">
         <v>45763</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="12">
         <v>45761</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
+      <c r="J5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="13"/>
+      <c r="L5" s="15">
+        <v>45812</v>
+      </c>
+      <c r="M5" s="28"/>
+      <c r="N5" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="9"/>
+      <c r="P5" s="9">
+        <v>45812</v>
+      </c>
+      <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="A6" s="8">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9">
+        <v>45798</v>
+      </c>
+      <c r="E6" s="12">
+        <v>45798</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9">
+        <v>45798</v>
+      </c>
+      <c r="I6" s="12">
+        <v>45798</v>
+      </c>
       <c r="L6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="N6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="8"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="15"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D7" s="3"/>
+      <c r="A7" s="8">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
+        <v>45805</v>
+      </c>
+      <c r="E7" s="12">
+        <v>45805</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="9">
+        <v>45812</v>
+      </c>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D8" s="3"/>
+      <c r="A8" s="8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
+        <v>45812</v>
+      </c>
+      <c r="E8" s="12">
+        <v>45809</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Team_Tasks.xlsx
+++ b/Team_Tasks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ELE_4\Prototype\Robotic_Car_TeamC1-HSHL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B389B3-6C67-415A-9544-1F2B382A33B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EEE094-BD6A-49CA-9BB5-77E6BC34012D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5115" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
   <si>
     <t>Milestone</t>
   </si>
@@ -119,13 +119,28 @@
   </si>
   <si>
     <t>ColorSensor holder</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
+    <t>Last Code Updates</t>
+  </si>
+  <si>
+    <t>Presentation If needed</t>
+  </si>
+  <si>
+    <t>Simulink</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,8 +185,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,6 +239,18 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -367,7 +400,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -405,15 +438,9 @@
     <xf numFmtId="16" fontId="3" fillId="7" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="3" fillId="7" borderId="9" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="8" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -450,7 +477,25 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="9" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -736,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
@@ -752,7 +797,7 @@
     <col min="11" max="11" width="9.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.08984375" style="2" customWidth="1"/>
     <col min="16" max="16" width="10.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
@@ -763,30 +808,30 @@
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="22" t="s">
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="25" t="s">
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="25"/>
     </row>
     <row r="2" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
@@ -878,7 +923,7 @@
       <c r="L3" s="9">
         <v>45763</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="13">
         <v>45761</v>
       </c>
       <c r="N3" s="8" t="s">
@@ -929,7 +974,7 @@
       <c r="L4" s="9">
         <v>45771</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>45771</v>
       </c>
       <c r="N4" s="8" t="s">
@@ -971,14 +1016,16 @@
       <c r="I5" s="12">
         <v>45761</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="15">
+      <c r="K5" s="31"/>
+      <c r="L5" s="32">
         <v>45812</v>
       </c>
-      <c r="M5" s="28"/>
+      <c r="M5" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="N5" s="8" t="s">
         <v>22</v>
       </c>
@@ -986,7 +1033,7 @@
       <c r="P5" s="9">
         <v>45812</v>
       </c>
-      <c r="Q5" s="15"/>
+      <c r="Q5" s="12"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
@@ -1017,8 +1064,10 @@
         <v>28</v>
       </c>
       <c r="O6" s="8"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="15"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
@@ -1041,21 +1090,55 @@
       <c r="H7" s="9">
         <v>45812</v>
       </c>
-      <c r="I7" s="13"/>
+      <c r="I7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="30"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="8">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="27"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9">
+      <c r="C9" s="8"/>
+      <c r="D9" s="9">
         <v>45812</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E9" s="12">
         <v>45809</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
